--- a/template/linearity_lbc.xlsx
+++ b/template/linearity_lbc.xlsx
@@ -87,7 +87,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="37">
+  <borders count="34">
     <border>
       <left/>
       <right/>
@@ -449,32 +449,11 @@
       <top style="medium"/>
       <bottom style="thin"/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="medium"/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="48" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -567,6 +546,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="48" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -583,8 +563,9 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="26" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -613,7 +594,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -1164,8 +1144,8 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="1.5"/>
-          <min val="-1.5"/>
+          <max val="0.5"/>
+          <min val="-0.5"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
@@ -1227,7 +1207,7 @@
         <crossAx val="10"/>
         <crosses val="autoZero"/>
         <crossBetween val="between"/>
-        <majorUnit val="0.25"/>
+        <majorUnit val="0.1"/>
       </valAx>
       <catAx>
         <axId val="1487964928"/>
@@ -1250,8 +1230,8 @@
         <axId val="1487965408"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="1.5"/>
-          <min val="-1.5"/>
+          <max val="0.5"/>
+          <min val="-0.5"/>
         </scaling>
         <delete val="0"/>
         <axPos val="r"/>
@@ -1321,7 +1301,7 @@
         <crossAx val="1487964928"/>
         <crosses val="max"/>
         <crossBetween val="between"/>
-        <majorUnit val="0.25"/>
+        <majorUnit val="0.1"/>
       </valAx>
     </plotArea>
     <legend>
@@ -1683,8 +1663,9 @@
           <t>Position　１LSB</t>
         </is>
       </c>
-      <c r="H3" s="47" t="n">
-        <v>0.00030517578125</v>
+      <c r="H3" s="48">
+        <f>IF(ABS(E7)&gt;3,160/2^19,160/SQRT(2)/2^19)</f>
+        <v/>
       </c>
     </row>
     <row r="5">
@@ -1710,14 +1691,14 @@
           <t>理論電圧(V)</t>
         </is>
       </c>
-      <c r="G5" s="48" t="inlineStr">
-        <is>
-          <t>対Position INL</t>
-        </is>
-      </c>
-      <c r="H5" s="49" t="inlineStr">
-        <is>
-          <t>対Position DNL</t>
+      <c r="G5" s="49" t="inlineStr">
+        <is>
+          <t>INL</t>
+        </is>
+      </c>
+      <c r="H5" s="50" t="inlineStr">
+        <is>
+          <t>DNL</t>
         </is>
       </c>
     </row>
@@ -1744,52 +1725,55 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="50" t="n">
+      <c r="A7" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="51" t="n">
+      <c r="B7" s="52" t="n">
         <v>-32768</v>
       </c>
-      <c r="C7" s="51" t="n">
+      <c r="C7" s="52" t="n">
         <v>0</v>
       </c>
-      <c r="D7" s="51" t="inlineStr">
+      <c r="D7" s="52" t="inlineStr">
         <is>
           <t>0000</t>
         </is>
       </c>
-      <c r="E7" s="52" t="n"/>
-      <c r="F7" s="52">
+      <c r="E7" s="53" t="n"/>
+      <c r="F7" s="53">
         <f>$F$3*C7+$E$7</f>
         <v/>
       </c>
-      <c r="G7" s="53">
+      <c r="G7" s="54">
         <f>(E7-F7)/$H$3</f>
         <v/>
       </c>
-      <c r="H7" s="54" t="n"/>
+      <c r="H7" s="55">
+        <f>G8-G7</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="50" t="n">
+      <c r="A8" s="51" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="51" t="n">
-        <v>-28673</v>
-      </c>
-      <c r="C8" s="51" t="n">
-        <v>4095</v>
-      </c>
-      <c r="D8" s="51" t="inlineStr">
-        <is>
-          <t>0FFF</t>
-        </is>
-      </c>
-      <c r="E8" s="52" t="n"/>
-      <c r="F8" s="52">
+      <c r="B8" s="52" t="n">
+        <v>-32767</v>
+      </c>
+      <c r="C8" s="52" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="52" t="inlineStr">
+        <is>
+          <t>0001</t>
+        </is>
+      </c>
+      <c r="E8" s="53" t="n"/>
+      <c r="F8" s="53">
         <f>$F$3*C8+$E$7</f>
         <v/>
       </c>
-      <c r="G8" s="53">
+      <c r="G8" s="54">
         <f>(E8-F8)/$H$3</f>
         <v/>
       </c>
@@ -1799,52 +1783,55 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="50" t="n">
+      <c r="A9" s="51" t="n">
         <v>3</v>
       </c>
-      <c r="B9" s="51" t="n">
-        <v>-28672</v>
-      </c>
-      <c r="C9" s="51" t="n">
-        <v>4096</v>
-      </c>
-      <c r="D9" s="51" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="E9" s="52" t="n"/>
-      <c r="F9" s="52">
+      <c r="B9" s="52" t="n">
+        <v>-32766</v>
+      </c>
+      <c r="C9" s="52" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" s="52" t="inlineStr">
+        <is>
+          <t>0002</t>
+        </is>
+      </c>
+      <c r="E9" s="53" t="n"/>
+      <c r="F9" s="53">
         <f>$F$3*C9+$E$7</f>
         <v/>
       </c>
-      <c r="G9" s="53">
+      <c r="G9" s="54">
         <f>(E9-F9)/$H$3</f>
         <v/>
       </c>
-      <c r="H9" s="54" t="n"/>
+      <c r="H9" s="55">
+        <f>G10-G9</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="50" t="n">
+      <c r="A10" s="51" t="n">
         <v>4</v>
       </c>
-      <c r="B10" s="51" t="n">
-        <v>-24577</v>
-      </c>
-      <c r="C10" s="51" t="n">
-        <v>8191</v>
-      </c>
-      <c r="D10" s="51" t="inlineStr">
-        <is>
-          <t>1FFF</t>
-        </is>
-      </c>
-      <c r="E10" s="52" t="n"/>
-      <c r="F10" s="52">
+      <c r="B10" s="52" t="n">
+        <v>-32765</v>
+      </c>
+      <c r="C10" s="52" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" s="52" t="inlineStr">
+        <is>
+          <t>0003</t>
+        </is>
+      </c>
+      <c r="E10" s="53" t="n"/>
+      <c r="F10" s="53">
         <f>$F$3*C10+$E$7</f>
         <v/>
       </c>
-      <c r="G10" s="53">
+      <c r="G10" s="54">
         <f>(E10-F10)/$H$3</f>
         <v/>
       </c>
@@ -1854,52 +1841,52 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="50" t="n">
+      <c r="A11" s="51" t="n">
         <v>5</v>
       </c>
-      <c r="B11" s="51" t="n">
-        <v>-24576</v>
-      </c>
-      <c r="C11" s="51" t="n">
-        <v>8192</v>
-      </c>
-      <c r="D11" s="51" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="E11" s="52" t="n"/>
-      <c r="F11" s="52">
+      <c r="B11" s="52" t="n">
+        <v>-32764</v>
+      </c>
+      <c r="C11" s="52" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" s="52" t="inlineStr">
+        <is>
+          <t>0004</t>
+        </is>
+      </c>
+      <c r="E11" s="53" t="n"/>
+      <c r="F11" s="53">
         <f>$F$3*C11+$E$7</f>
         <v/>
       </c>
-      <c r="G11" s="53">
+      <c r="G11" s="54">
         <f>(E11-F11)/$H$3</f>
         <v/>
       </c>
-      <c r="H11" s="54" t="n"/>
+      <c r="H11" s="56" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="50" t="n">
+      <c r="A12" s="51" t="n">
         <v>6</v>
       </c>
-      <c r="B12" s="51" t="n">
-        <v>-20481</v>
-      </c>
-      <c r="C12" s="51" t="n">
-        <v>12287</v>
-      </c>
-      <c r="D12" s="51" t="inlineStr">
-        <is>
-          <t>2FFF</t>
-        </is>
-      </c>
-      <c r="E12" s="52" t="n"/>
-      <c r="F12" s="52">
+      <c r="B12" s="52" t="n">
+        <v>-32761</v>
+      </c>
+      <c r="C12" s="52" t="n">
+        <v>7</v>
+      </c>
+      <c r="D12" s="52" t="inlineStr">
+        <is>
+          <t>0007</t>
+        </is>
+      </c>
+      <c r="E12" s="53" t="n"/>
+      <c r="F12" s="53">
         <f>$F$3*C12+$E$7</f>
         <v/>
       </c>
-      <c r="G12" s="53">
+      <c r="G12" s="54">
         <f>(E12-F12)/$H$3</f>
         <v/>
       </c>
@@ -1909,52 +1896,52 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="50" t="n">
+      <c r="A13" s="51" t="n">
         <v>7</v>
       </c>
-      <c r="B13" s="51" t="n">
-        <v>-20480</v>
-      </c>
-      <c r="C13" s="51" t="n">
-        <v>12288</v>
-      </c>
-      <c r="D13" s="51" t="inlineStr">
-        <is>
-          <t>3000</t>
-        </is>
-      </c>
-      <c r="E13" s="52" t="n"/>
-      <c r="F13" s="52">
+      <c r="B13" s="52" t="n">
+        <v>-32760</v>
+      </c>
+      <c r="C13" s="52" t="n">
+        <v>8</v>
+      </c>
+      <c r="D13" s="52" t="inlineStr">
+        <is>
+          <t>0008</t>
+        </is>
+      </c>
+      <c r="E13" s="53" t="n"/>
+      <c r="F13" s="53">
         <f>$F$3*C13+$E$7</f>
         <v/>
       </c>
-      <c r="G13" s="53">
+      <c r="G13" s="54">
         <f>(E13-F13)/$H$3</f>
         <v/>
       </c>
-      <c r="H13" s="54" t="n"/>
+      <c r="H13" s="56" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="50" t="n">
+      <c r="A14" s="51" t="n">
         <v>8</v>
       </c>
-      <c r="B14" s="51" t="n">
-        <v>-16385</v>
-      </c>
-      <c r="C14" s="51" t="n">
-        <v>16383</v>
-      </c>
-      <c r="D14" s="51" t="inlineStr">
-        <is>
-          <t>3FFF</t>
-        </is>
-      </c>
-      <c r="E14" s="52" t="n"/>
-      <c r="F14" s="52">
+      <c r="B14" s="52" t="n">
+        <v>-32753</v>
+      </c>
+      <c r="C14" s="52" t="n">
+        <v>15</v>
+      </c>
+      <c r="D14" s="52" t="inlineStr">
+        <is>
+          <t>000F</t>
+        </is>
+      </c>
+      <c r="E14" s="53" t="n"/>
+      <c r="F14" s="53">
         <f>$F$3*C14+$E$7</f>
         <v/>
       </c>
-      <c r="G14" s="53">
+      <c r="G14" s="54">
         <f>(E14-F14)/$H$3</f>
         <v/>
       </c>
@@ -1964,52 +1951,52 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="50" t="n">
+      <c r="A15" s="51" t="n">
         <v>9</v>
       </c>
-      <c r="B15" s="51" t="n">
-        <v>-16384</v>
-      </c>
-      <c r="C15" s="51" t="n">
-        <v>16384</v>
-      </c>
-      <c r="D15" s="51" t="inlineStr">
-        <is>
-          <t>4000</t>
-        </is>
-      </c>
-      <c r="E15" s="52" t="n"/>
-      <c r="F15" s="52">
+      <c r="B15" s="52" t="n">
+        <v>-32752</v>
+      </c>
+      <c r="C15" s="52" t="n">
+        <v>16</v>
+      </c>
+      <c r="D15" s="52" t="inlineStr">
+        <is>
+          <t>0010</t>
+        </is>
+      </c>
+      <c r="E15" s="53" t="n"/>
+      <c r="F15" s="53">
         <f>$F$3*C15+$E$7</f>
         <v/>
       </c>
-      <c r="G15" s="53">
+      <c r="G15" s="54">
         <f>(E15-F15)/$H$3</f>
         <v/>
       </c>
-      <c r="H15" s="54" t="n"/>
+      <c r="H15" s="56" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="50" t="n">
+      <c r="A16" s="51" t="n">
         <v>10</v>
       </c>
-      <c r="B16" s="51" t="n">
-        <v>-12289</v>
-      </c>
-      <c r="C16" s="51" t="n">
-        <v>20479</v>
-      </c>
-      <c r="D16" s="51" t="inlineStr">
-        <is>
-          <t>4FFF</t>
-        </is>
-      </c>
-      <c r="E16" s="52" t="n"/>
-      <c r="F16" s="52">
+      <c r="B16" s="52" t="n">
+        <v>-32737</v>
+      </c>
+      <c r="C16" s="52" t="n">
+        <v>31</v>
+      </c>
+      <c r="D16" s="52" t="inlineStr">
+        <is>
+          <t>001F</t>
+        </is>
+      </c>
+      <c r="E16" s="53" t="n"/>
+      <c r="F16" s="53">
         <f>$F$3*C16+$E$7</f>
         <v/>
       </c>
-      <c r="G16" s="53">
+      <c r="G16" s="54">
         <f>(E16-F16)/$H$3</f>
         <v/>
       </c>
@@ -2019,52 +2006,52 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="50" t="n">
+      <c r="A17" s="51" t="n">
         <v>11</v>
       </c>
-      <c r="B17" s="51" t="n">
-        <v>-12288</v>
-      </c>
-      <c r="C17" s="51" t="n">
-        <v>20480</v>
-      </c>
-      <c r="D17" s="51" t="inlineStr">
-        <is>
-          <t>5000</t>
-        </is>
-      </c>
-      <c r="E17" s="52" t="n"/>
-      <c r="F17" s="52">
+      <c r="B17" s="52" t="n">
+        <v>-32736</v>
+      </c>
+      <c r="C17" s="52" t="n">
+        <v>32</v>
+      </c>
+      <c r="D17" s="52" t="inlineStr">
+        <is>
+          <t>0020</t>
+        </is>
+      </c>
+      <c r="E17" s="53" t="n"/>
+      <c r="F17" s="53">
         <f>$F$3*C17+$E$7</f>
         <v/>
       </c>
-      <c r="G17" s="53">
+      <c r="G17" s="54">
         <f>(E17-F17)/$H$3</f>
         <v/>
       </c>
-      <c r="H17" s="54" t="n"/>
+      <c r="H17" s="56" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="50" t="n">
+      <c r="A18" s="51" t="n">
         <v>12</v>
       </c>
-      <c r="B18" s="51" t="n">
-        <v>-8193</v>
-      </c>
-      <c r="C18" s="51" t="n">
-        <v>24575</v>
-      </c>
-      <c r="D18" s="51" t="inlineStr">
-        <is>
-          <t>5FFF</t>
-        </is>
-      </c>
-      <c r="E18" s="52" t="n"/>
-      <c r="F18" s="52">
+      <c r="B18" s="52" t="n">
+        <v>-32705</v>
+      </c>
+      <c r="C18" s="52" t="n">
+        <v>63</v>
+      </c>
+      <c r="D18" s="52" t="inlineStr">
+        <is>
+          <t>003F</t>
+        </is>
+      </c>
+      <c r="E18" s="53" t="n"/>
+      <c r="F18" s="53">
         <f>$F$3*C18+$E$7</f>
         <v/>
       </c>
-      <c r="G18" s="53">
+      <c r="G18" s="54">
         <f>(E18-F18)/$H$3</f>
         <v/>
       </c>
@@ -2074,52 +2061,52 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="50" t="n">
+      <c r="A19" s="51" t="n">
         <v>13</v>
       </c>
-      <c r="B19" s="51" t="n">
-        <v>-8192</v>
-      </c>
-      <c r="C19" s="51" t="n">
-        <v>24576</v>
-      </c>
-      <c r="D19" s="51" t="inlineStr">
-        <is>
-          <t>6000</t>
-        </is>
-      </c>
-      <c r="E19" s="52" t="n"/>
-      <c r="F19" s="52">
+      <c r="B19" s="52" t="n">
+        <v>-32704</v>
+      </c>
+      <c r="C19" s="52" t="n">
+        <v>64</v>
+      </c>
+      <c r="D19" s="52" t="inlineStr">
+        <is>
+          <t>0040</t>
+        </is>
+      </c>
+      <c r="E19" s="53" t="n"/>
+      <c r="F19" s="53">
         <f>$F$3*C19+$E$7</f>
         <v/>
       </c>
-      <c r="G19" s="53">
+      <c r="G19" s="54">
         <f>(E19-F19)/$H$3</f>
         <v/>
       </c>
-      <c r="H19" s="54" t="n"/>
+      <c r="H19" s="56" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="50" t="n">
+      <c r="A20" s="51" t="n">
         <v>14</v>
       </c>
-      <c r="B20" s="51" t="n">
-        <v>-4097</v>
-      </c>
-      <c r="C20" s="51" t="n">
-        <v>28671</v>
-      </c>
-      <c r="D20" s="51" t="inlineStr">
-        <is>
-          <t>6FFF</t>
-        </is>
-      </c>
-      <c r="E20" s="52" t="n"/>
-      <c r="F20" s="52">
+      <c r="B20" s="52" t="n">
+        <v>-32641</v>
+      </c>
+      <c r="C20" s="52" t="n">
+        <v>127</v>
+      </c>
+      <c r="D20" s="52" t="inlineStr">
+        <is>
+          <t>007F</t>
+        </is>
+      </c>
+      <c r="E20" s="53" t="n"/>
+      <c r="F20" s="53">
         <f>$F$3*C20+$E$7</f>
         <v/>
       </c>
-      <c r="G20" s="53">
+      <c r="G20" s="54">
         <f>(E20-F20)/$H$3</f>
         <v/>
       </c>
@@ -2129,52 +2116,52 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="50" t="n">
+      <c r="A21" s="51" t="n">
         <v>15</v>
       </c>
-      <c r="B21" s="51" t="n">
-        <v>-4096</v>
-      </c>
-      <c r="C21" s="51" t="n">
-        <v>28672</v>
-      </c>
-      <c r="D21" s="51" t="inlineStr">
-        <is>
-          <t>7000</t>
-        </is>
-      </c>
-      <c r="E21" s="52" t="n"/>
-      <c r="F21" s="52">
+      <c r="B21" s="52" t="n">
+        <v>-32640</v>
+      </c>
+      <c r="C21" s="52" t="n">
+        <v>128</v>
+      </c>
+      <c r="D21" s="52" t="inlineStr">
+        <is>
+          <t>0080</t>
+        </is>
+      </c>
+      <c r="E21" s="53" t="n"/>
+      <c r="F21" s="53">
         <f>$F$3*C21+$E$7</f>
         <v/>
       </c>
-      <c r="G21" s="53">
+      <c r="G21" s="54">
         <f>(E21-F21)/$H$3</f>
         <v/>
       </c>
-      <c r="H21" s="54" t="n"/>
+      <c r="H21" s="56" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="50" t="n">
+      <c r="A22" s="51" t="n">
         <v>16</v>
       </c>
-      <c r="B22" s="51" t="n">
-        <v>-1</v>
-      </c>
-      <c r="C22" s="51" t="n">
-        <v>32767</v>
-      </c>
-      <c r="D22" s="51" t="inlineStr">
-        <is>
-          <t>7FFF</t>
-        </is>
-      </c>
-      <c r="E22" s="52" t="n"/>
-      <c r="F22" s="52">
+      <c r="B22" s="52" t="n">
+        <v>-32513</v>
+      </c>
+      <c r="C22" s="52" t="n">
+        <v>255</v>
+      </c>
+      <c r="D22" s="52" t="inlineStr">
+        <is>
+          <t>00FF</t>
+        </is>
+      </c>
+      <c r="E22" s="53" t="n"/>
+      <c r="F22" s="53">
         <f>$F$3*C22+$E$7</f>
         <v/>
       </c>
-      <c r="G22" s="53">
+      <c r="G22" s="54">
         <f>(E22-F22)/$H$3</f>
         <v/>
       </c>
@@ -2184,52 +2171,52 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="50" t="n">
+      <c r="A23" s="51" t="n">
         <v>17</v>
       </c>
-      <c r="B23" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" s="51" t="n">
-        <v>32768</v>
-      </c>
-      <c r="D23" s="51" t="inlineStr">
-        <is>
-          <t>8000</t>
-        </is>
-      </c>
-      <c r="E23" s="52" t="n"/>
-      <c r="F23" s="52">
+      <c r="B23" s="52" t="n">
+        <v>-32512</v>
+      </c>
+      <c r="C23" s="52" t="n">
+        <v>256</v>
+      </c>
+      <c r="D23" s="52" t="inlineStr">
+        <is>
+          <t>0100</t>
+        </is>
+      </c>
+      <c r="E23" s="53" t="n"/>
+      <c r="F23" s="53">
         <f>$F$3*C23+$E$7</f>
         <v/>
       </c>
-      <c r="G23" s="53">
+      <c r="G23" s="54">
         <f>(E23-F23)/$H$3</f>
         <v/>
       </c>
-      <c r="H23" s="54" t="n"/>
+      <c r="H23" s="56" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="50" t="n">
+      <c r="A24" s="51" t="n">
         <v>18</v>
       </c>
-      <c r="B24" s="51" t="n">
-        <v>4095</v>
-      </c>
-      <c r="C24" s="51" t="n">
-        <v>36863</v>
-      </c>
-      <c r="D24" s="51" t="inlineStr">
-        <is>
-          <t>8FFF</t>
-        </is>
-      </c>
-      <c r="E24" s="52" t="n"/>
-      <c r="F24" s="52">
+      <c r="B24" s="52" t="n">
+        <v>-32257</v>
+      </c>
+      <c r="C24" s="52" t="n">
+        <v>511</v>
+      </c>
+      <c r="D24" s="52" t="inlineStr">
+        <is>
+          <t>01FF</t>
+        </is>
+      </c>
+      <c r="E24" s="53" t="n"/>
+      <c r="F24" s="53">
         <f>$F$3*C24+$E$7</f>
         <v/>
       </c>
-      <c r="G24" s="53">
+      <c r="G24" s="54">
         <f>(E24-F24)/$H$3</f>
         <v/>
       </c>
@@ -2239,52 +2226,52 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="50" t="n">
+      <c r="A25" s="51" t="n">
         <v>19</v>
       </c>
-      <c r="B25" s="51" t="n">
-        <v>4096</v>
-      </c>
-      <c r="C25" s="51" t="n">
-        <v>36864</v>
-      </c>
-      <c r="D25" s="51" t="inlineStr">
-        <is>
-          <t>9000</t>
-        </is>
-      </c>
-      <c r="E25" s="52" t="n"/>
-      <c r="F25" s="52">
+      <c r="B25" s="52" t="n">
+        <v>-32256</v>
+      </c>
+      <c r="C25" s="52" t="n">
+        <v>512</v>
+      </c>
+      <c r="D25" s="52" t="inlineStr">
+        <is>
+          <t>0200</t>
+        </is>
+      </c>
+      <c r="E25" s="53" t="n"/>
+      <c r="F25" s="53">
         <f>$F$3*C25+$E$7</f>
         <v/>
       </c>
-      <c r="G25" s="53">
+      <c r="G25" s="54">
         <f>(E25-F25)/$H$3</f>
         <v/>
       </c>
-      <c r="H25" s="54" t="n"/>
+      <c r="H25" s="56" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="50" t="n">
+      <c r="A26" s="51" t="n">
         <v>20</v>
       </c>
-      <c r="B26" s="51" t="n">
-        <v>8191</v>
-      </c>
-      <c r="C26" s="51" t="n">
-        <v>40959</v>
-      </c>
-      <c r="D26" s="51" t="inlineStr">
-        <is>
-          <t>9FFF</t>
-        </is>
-      </c>
-      <c r="E26" s="52" t="n"/>
-      <c r="F26" s="52">
+      <c r="B26" s="52" t="n">
+        <v>-31745</v>
+      </c>
+      <c r="C26" s="52" t="n">
+        <v>1023</v>
+      </c>
+      <c r="D26" s="52" t="inlineStr">
+        <is>
+          <t>03FF</t>
+        </is>
+      </c>
+      <c r="E26" s="53" t="n"/>
+      <c r="F26" s="53">
         <f>$F$3*C26+$E$7</f>
         <v/>
       </c>
-      <c r="G26" s="53">
+      <c r="G26" s="54">
         <f>(E26-F26)/$H$3</f>
         <v/>
       </c>
@@ -2294,52 +2281,52 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="50" t="n">
+      <c r="A27" s="51" t="n">
         <v>21</v>
       </c>
-      <c r="B27" s="51" t="n">
-        <v>8192</v>
-      </c>
-      <c r="C27" s="51" t="n">
-        <v>40960</v>
-      </c>
-      <c r="D27" s="51" t="inlineStr">
-        <is>
-          <t>A000</t>
-        </is>
-      </c>
-      <c r="E27" s="52" t="n"/>
-      <c r="F27" s="52">
+      <c r="B27" s="52" t="n">
+        <v>-31744</v>
+      </c>
+      <c r="C27" s="52" t="n">
+        <v>1024</v>
+      </c>
+      <c r="D27" s="52" t="inlineStr">
+        <is>
+          <t>0400</t>
+        </is>
+      </c>
+      <c r="E27" s="53" t="n"/>
+      <c r="F27" s="53">
         <f>$F$3*C27+$E$7</f>
         <v/>
       </c>
-      <c r="G27" s="53">
+      <c r="G27" s="54">
         <f>(E27-F27)/$H$3</f>
         <v/>
       </c>
-      <c r="H27" s="54" t="n"/>
+      <c r="H27" s="56" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="50" t="n">
+      <c r="A28" s="51" t="n">
         <v>22</v>
       </c>
-      <c r="B28" s="51" t="n">
-        <v>12287</v>
-      </c>
-      <c r="C28" s="51" t="n">
-        <v>45055</v>
-      </c>
-      <c r="D28" s="51" t="inlineStr">
-        <is>
-          <t>AFFF</t>
-        </is>
-      </c>
-      <c r="E28" s="52" t="n"/>
-      <c r="F28" s="52">
+      <c r="B28" s="52" t="n">
+        <v>-30721</v>
+      </c>
+      <c r="C28" s="52" t="n">
+        <v>2047</v>
+      </c>
+      <c r="D28" s="52" t="inlineStr">
+        <is>
+          <t>07FF</t>
+        </is>
+      </c>
+      <c r="E28" s="53" t="n"/>
+      <c r="F28" s="53">
         <f>$F$3*C28+$E$7</f>
         <v/>
       </c>
-      <c r="G28" s="53">
+      <c r="G28" s="54">
         <f>(E28-F28)/$H$3</f>
         <v/>
       </c>
@@ -2349,52 +2336,52 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="50" t="n">
+      <c r="A29" s="51" t="n">
         <v>23</v>
       </c>
-      <c r="B29" s="51" t="n">
-        <v>12288</v>
-      </c>
-      <c r="C29" s="51" t="n">
-        <v>45056</v>
-      </c>
-      <c r="D29" s="51" t="inlineStr">
-        <is>
-          <t>B000</t>
-        </is>
-      </c>
-      <c r="E29" s="52" t="n"/>
-      <c r="F29" s="52">
+      <c r="B29" s="52" t="n">
+        <v>-30720</v>
+      </c>
+      <c r="C29" s="52" t="n">
+        <v>2048</v>
+      </c>
+      <c r="D29" s="52" t="inlineStr">
+        <is>
+          <t>0800</t>
+        </is>
+      </c>
+      <c r="E29" s="53" t="n"/>
+      <c r="F29" s="53">
         <f>$F$3*C29+$E$7</f>
         <v/>
       </c>
-      <c r="G29" s="53">
+      <c r="G29" s="54">
         <f>(E29-F29)/$H$3</f>
         <v/>
       </c>
-      <c r="H29" s="54" t="n"/>
+      <c r="H29" s="56" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="50" t="n">
+      <c r="A30" s="51" t="n">
         <v>24</v>
       </c>
-      <c r="B30" s="51" t="n">
-        <v>16383</v>
-      </c>
-      <c r="C30" s="51" t="n">
-        <v>49151</v>
-      </c>
-      <c r="D30" s="51" t="inlineStr">
-        <is>
-          <t>BFFF</t>
-        </is>
-      </c>
-      <c r="E30" s="52" t="n"/>
-      <c r="F30" s="52">
+      <c r="B30" s="52" t="n">
+        <v>-28673</v>
+      </c>
+      <c r="C30" s="52" t="n">
+        <v>4095</v>
+      </c>
+      <c r="D30" s="52" t="inlineStr">
+        <is>
+          <t>0FFF</t>
+        </is>
+      </c>
+      <c r="E30" s="53" t="n"/>
+      <c r="F30" s="53">
         <f>$F$3*C30+$E$7</f>
         <v/>
       </c>
-      <c r="G30" s="53">
+      <c r="G30" s="54">
         <f>(E30-F30)/$H$3</f>
         <v/>
       </c>
@@ -2404,52 +2391,52 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="50" t="n">
+      <c r="A31" s="51" t="n">
         <v>25</v>
       </c>
-      <c r="B31" s="51" t="n">
-        <v>16384</v>
-      </c>
-      <c r="C31" s="51" t="n">
-        <v>49152</v>
-      </c>
-      <c r="D31" s="51" t="inlineStr">
-        <is>
-          <t>C000</t>
-        </is>
-      </c>
-      <c r="E31" s="52" t="n"/>
-      <c r="F31" s="52">
+      <c r="B31" s="52" t="n">
+        <v>-28672</v>
+      </c>
+      <c r="C31" s="52" t="n">
+        <v>4096</v>
+      </c>
+      <c r="D31" s="52" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="E31" s="53" t="n"/>
+      <c r="F31" s="53">
         <f>$F$3*C31+$E$7</f>
         <v/>
       </c>
-      <c r="G31" s="53">
+      <c r="G31" s="54">
         <f>(E31-F31)/$H$3</f>
         <v/>
       </c>
-      <c r="H31" s="54" t="n"/>
+      <c r="H31" s="56" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="50" t="n">
+      <c r="A32" s="51" t="n">
         <v>26</v>
       </c>
-      <c r="B32" s="51" t="n">
-        <v>20479</v>
-      </c>
-      <c r="C32" s="51" t="n">
-        <v>53247</v>
-      </c>
-      <c r="D32" s="51" t="inlineStr">
-        <is>
-          <t>CFFF</t>
-        </is>
-      </c>
-      <c r="E32" s="52" t="n"/>
-      <c r="F32" s="52">
+      <c r="B32" s="52" t="n">
+        <v>-24577</v>
+      </c>
+      <c r="C32" s="52" t="n">
+        <v>8191</v>
+      </c>
+      <c r="D32" s="52" t="inlineStr">
+        <is>
+          <t>1FFF</t>
+        </is>
+      </c>
+      <c r="E32" s="53" t="n"/>
+      <c r="F32" s="53">
         <f>$F$3*C32+$E$7</f>
         <v/>
       </c>
-      <c r="G32" s="53">
+      <c r="G32" s="54">
         <f>(E32-F32)/$H$3</f>
         <v/>
       </c>
@@ -2459,52 +2446,52 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="50" t="n">
+      <c r="A33" s="51" t="n">
         <v>27</v>
       </c>
-      <c r="B33" s="51" t="n">
-        <v>20480</v>
-      </c>
-      <c r="C33" s="51" t="n">
-        <v>53248</v>
-      </c>
-      <c r="D33" s="51" t="inlineStr">
-        <is>
-          <t>D000</t>
-        </is>
-      </c>
-      <c r="E33" s="52" t="n"/>
-      <c r="F33" s="52">
+      <c r="B33" s="52" t="n">
+        <v>-24576</v>
+      </c>
+      <c r="C33" s="52" t="n">
+        <v>8192</v>
+      </c>
+      <c r="D33" s="52" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="E33" s="53" t="n"/>
+      <c r="F33" s="53">
         <f>$F$3*C33+$E$7</f>
         <v/>
       </c>
-      <c r="G33" s="53">
+      <c r="G33" s="54">
         <f>(E33-F33)/$H$3</f>
         <v/>
       </c>
-      <c r="H33" s="54" t="n"/>
+      <c r="H33" s="56" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="50" t="n">
+      <c r="A34" s="51" t="n">
         <v>28</v>
       </c>
-      <c r="B34" s="51" t="n">
-        <v>24575</v>
-      </c>
-      <c r="C34" s="51" t="n">
-        <v>57343</v>
-      </c>
-      <c r="D34" s="51" t="inlineStr">
-        <is>
-          <t>DFFF</t>
-        </is>
-      </c>
-      <c r="E34" s="52" t="n"/>
-      <c r="F34" s="52">
+      <c r="B34" s="52" t="n">
+        <v>-20481</v>
+      </c>
+      <c r="C34" s="52" t="n">
+        <v>12287</v>
+      </c>
+      <c r="D34" s="52" t="inlineStr">
+        <is>
+          <t>2FFF</t>
+        </is>
+      </c>
+      <c r="E34" s="53" t="n"/>
+      <c r="F34" s="53">
         <f>$F$3*C34+$E$7</f>
         <v/>
       </c>
-      <c r="G34" s="53">
+      <c r="G34" s="54">
         <f>(E34-F34)/$H$3</f>
         <v/>
       </c>
@@ -2514,52 +2501,52 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="50" t="n">
+      <c r="A35" s="51" t="n">
         <v>29</v>
       </c>
-      <c r="B35" s="51" t="n">
-        <v>24576</v>
-      </c>
-      <c r="C35" s="51" t="n">
-        <v>57344</v>
-      </c>
-      <c r="D35" s="51" t="inlineStr">
-        <is>
-          <t>E000</t>
-        </is>
-      </c>
-      <c r="E35" s="52" t="n"/>
-      <c r="F35" s="52">
+      <c r="B35" s="52" t="n">
+        <v>-20480</v>
+      </c>
+      <c r="C35" s="52" t="n">
+        <v>12288</v>
+      </c>
+      <c r="D35" s="52" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="E35" s="53" t="n"/>
+      <c r="F35" s="53">
         <f>$F$3*C35+$E$7</f>
         <v/>
       </c>
-      <c r="G35" s="53">
+      <c r="G35" s="54">
         <f>(E35-F35)/$H$3</f>
         <v/>
       </c>
-      <c r="H35" s="54" t="n"/>
+      <c r="H35" s="56" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="50" t="n">
+      <c r="A36" s="51" t="n">
         <v>30</v>
       </c>
-      <c r="B36" s="51" t="n">
-        <v>28671</v>
-      </c>
-      <c r="C36" s="51" t="n">
-        <v>61439</v>
-      </c>
-      <c r="D36" s="51" t="inlineStr">
-        <is>
-          <t>EFFF</t>
-        </is>
-      </c>
-      <c r="E36" s="52" t="n"/>
-      <c r="F36" s="52">
+      <c r="B36" s="52" t="n">
+        <v>-16385</v>
+      </c>
+      <c r="C36" s="52" t="n">
+        <v>16383</v>
+      </c>
+      <c r="D36" s="52" t="inlineStr">
+        <is>
+          <t>3FFF</t>
+        </is>
+      </c>
+      <c r="E36" s="53" t="n"/>
+      <c r="F36" s="53">
         <f>$F$3*C36+$E$7</f>
         <v/>
       </c>
-      <c r="G36" s="53">
+      <c r="G36" s="54">
         <f>(E36-F36)/$H$3</f>
         <v/>
       </c>
@@ -2569,52 +2556,52 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="50" t="n">
+      <c r="A37" s="51" t="n">
         <v>31</v>
       </c>
-      <c r="B37" s="51" t="n">
-        <v>28672</v>
-      </c>
-      <c r="C37" s="51" t="n">
-        <v>61440</v>
-      </c>
-      <c r="D37" s="51" t="inlineStr">
-        <is>
-          <t>F000</t>
-        </is>
-      </c>
-      <c r="E37" s="52" t="n"/>
-      <c r="F37" s="52">
+      <c r="B37" s="52" t="n">
+        <v>-16384</v>
+      </c>
+      <c r="C37" s="52" t="n">
+        <v>16384</v>
+      </c>
+      <c r="D37" s="52" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="E37" s="53" t="n"/>
+      <c r="F37" s="53">
         <f>$F$3*C37+$E$7</f>
         <v/>
       </c>
-      <c r="G37" s="53">
+      <c r="G37" s="54">
         <f>(E37-F37)/$H$3</f>
         <v/>
       </c>
-      <c r="H37" s="54" t="n"/>
+      <c r="H37" s="56" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="50" t="n">
+      <c r="A38" s="51" t="n">
         <v>32</v>
       </c>
-      <c r="B38" s="51" t="n">
-        <v>30719</v>
-      </c>
-      <c r="C38" s="51" t="n">
-        <v>63487</v>
-      </c>
-      <c r="D38" s="51" t="inlineStr">
-        <is>
-          <t>F7FF</t>
-        </is>
-      </c>
-      <c r="E38" s="52" t="n"/>
-      <c r="F38" s="52">
+      <c r="B38" s="52" t="n">
+        <v>-12289</v>
+      </c>
+      <c r="C38" s="52" t="n">
+        <v>20479</v>
+      </c>
+      <c r="D38" s="52" t="inlineStr">
+        <is>
+          <t>4FFF</t>
+        </is>
+      </c>
+      <c r="E38" s="53" t="n"/>
+      <c r="F38" s="53">
         <f>$F$3*C38+$E$7</f>
         <v/>
       </c>
-      <c r="G38" s="53">
+      <c r="G38" s="54">
         <f>(E38-F38)/$H$3</f>
         <v/>
       </c>
@@ -2624,52 +2611,52 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="50" t="n">
+      <c r="A39" s="51" t="n">
         <v>33</v>
       </c>
-      <c r="B39" s="51" t="n">
-        <v>30720</v>
-      </c>
-      <c r="C39" s="51" t="n">
-        <v>63488</v>
-      </c>
-      <c r="D39" s="51" t="inlineStr">
-        <is>
-          <t>F800</t>
-        </is>
-      </c>
-      <c r="E39" s="52" t="n"/>
-      <c r="F39" s="52">
+      <c r="B39" s="52" t="n">
+        <v>-12288</v>
+      </c>
+      <c r="C39" s="52" t="n">
+        <v>20480</v>
+      </c>
+      <c r="D39" s="52" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
+      <c r="E39" s="53" t="n"/>
+      <c r="F39" s="53">
         <f>$F$3*C39+$E$7</f>
         <v/>
       </c>
-      <c r="G39" s="53">
+      <c r="G39" s="54">
         <f>(E39-F39)/$H$3</f>
         <v/>
       </c>
-      <c r="H39" s="54" t="n"/>
+      <c r="H39" s="56" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="50" t="n">
+      <c r="A40" s="51" t="n">
         <v>34</v>
       </c>
-      <c r="B40" s="51" t="n">
-        <v>31743</v>
-      </c>
-      <c r="C40" s="51" t="n">
-        <v>64511</v>
-      </c>
-      <c r="D40" s="51" t="inlineStr">
-        <is>
-          <t>FBFF</t>
-        </is>
-      </c>
-      <c r="E40" s="52" t="n"/>
-      <c r="F40" s="52">
+      <c r="B40" s="52" t="n">
+        <v>-8193</v>
+      </c>
+      <c r="C40" s="52" t="n">
+        <v>24575</v>
+      </c>
+      <c r="D40" s="52" t="inlineStr">
+        <is>
+          <t>5FFF</t>
+        </is>
+      </c>
+      <c r="E40" s="53" t="n"/>
+      <c r="F40" s="53">
         <f>$F$3*C40+$E$7</f>
         <v/>
       </c>
-      <c r="G40" s="53">
+      <c r="G40" s="54">
         <f>(E40-F40)/$H$3</f>
         <v/>
       </c>
@@ -2679,52 +2666,52 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="50" t="n">
+      <c r="A41" s="51" t="n">
         <v>35</v>
       </c>
-      <c r="B41" s="51" t="n">
-        <v>31744</v>
-      </c>
-      <c r="C41" s="51" t="n">
-        <v>64512</v>
-      </c>
-      <c r="D41" s="51" t="inlineStr">
-        <is>
-          <t>FC00</t>
-        </is>
-      </c>
-      <c r="E41" s="52" t="n"/>
-      <c r="F41" s="52">
+      <c r="B41" s="52" t="n">
+        <v>-8192</v>
+      </c>
+      <c r="C41" s="52" t="n">
+        <v>24576</v>
+      </c>
+      <c r="D41" s="52" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="E41" s="53" t="n"/>
+      <c r="F41" s="53">
         <f>$F$3*C41+$E$7</f>
         <v/>
       </c>
-      <c r="G41" s="53">
+      <c r="G41" s="54">
         <f>(E41-F41)/$H$3</f>
         <v/>
       </c>
-      <c r="H41" s="54" t="n"/>
+      <c r="H41" s="56" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="50" t="n">
+      <c r="A42" s="51" t="n">
         <v>36</v>
       </c>
-      <c r="B42" s="51" t="n">
-        <v>32255</v>
-      </c>
-      <c r="C42" s="51" t="n">
-        <v>65023</v>
-      </c>
-      <c r="D42" s="51" t="inlineStr">
-        <is>
-          <t>FDFF</t>
-        </is>
-      </c>
-      <c r="E42" s="52" t="n"/>
-      <c r="F42" s="52">
+      <c r="B42" s="52" t="n">
+        <v>-4097</v>
+      </c>
+      <c r="C42" s="52" t="n">
+        <v>28671</v>
+      </c>
+      <c r="D42" s="52" t="inlineStr">
+        <is>
+          <t>6FFF</t>
+        </is>
+      </c>
+      <c r="E42" s="53" t="n"/>
+      <c r="F42" s="53">
         <f>$F$3*C42+$E$7</f>
         <v/>
       </c>
-      <c r="G42" s="53">
+      <c r="G42" s="54">
         <f>(E42-F42)/$H$3</f>
         <v/>
       </c>
@@ -2734,52 +2721,52 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="50" t="n">
+      <c r="A43" s="51" t="n">
         <v>37</v>
       </c>
-      <c r="B43" s="51" t="n">
-        <v>32256</v>
-      </c>
-      <c r="C43" s="51" t="n">
-        <v>65024</v>
-      </c>
-      <c r="D43" s="51" t="inlineStr">
-        <is>
-          <t>FE00</t>
-        </is>
-      </c>
-      <c r="E43" s="52" t="n"/>
-      <c r="F43" s="52">
+      <c r="B43" s="52" t="n">
+        <v>-4096</v>
+      </c>
+      <c r="C43" s="52" t="n">
+        <v>28672</v>
+      </c>
+      <c r="D43" s="52" t="inlineStr">
+        <is>
+          <t>7000</t>
+        </is>
+      </c>
+      <c r="E43" s="53" t="n"/>
+      <c r="F43" s="53">
         <f>$F$3*C43+$E$7</f>
         <v/>
       </c>
-      <c r="G43" s="53">
+      <c r="G43" s="54">
         <f>(E43-F43)/$H$3</f>
         <v/>
       </c>
-      <c r="H43" s="54" t="n"/>
+      <c r="H43" s="56" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="50" t="n">
+      <c r="A44" s="51" t="n">
         <v>38</v>
       </c>
-      <c r="B44" s="51" t="n">
-        <v>32511</v>
-      </c>
-      <c r="C44" s="51" t="n">
-        <v>65279</v>
-      </c>
-      <c r="D44" s="51" t="inlineStr">
-        <is>
-          <t>FEFF</t>
-        </is>
-      </c>
-      <c r="E44" s="52" t="n"/>
-      <c r="F44" s="52">
+      <c r="B44" s="52" t="n">
+        <v>-1</v>
+      </c>
+      <c r="C44" s="52" t="n">
+        <v>32767</v>
+      </c>
+      <c r="D44" s="52" t="inlineStr">
+        <is>
+          <t>7FFF</t>
+        </is>
+      </c>
+      <c r="E44" s="53" t="n"/>
+      <c r="F44" s="53">
         <f>$F$3*C44+$E$7</f>
         <v/>
       </c>
-      <c r="G44" s="53">
+      <c r="G44" s="54">
         <f>(E44-F44)/$H$3</f>
         <v/>
       </c>
@@ -2789,52 +2776,52 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="50" t="n">
+      <c r="A45" s="51" t="n">
         <v>39</v>
       </c>
-      <c r="B45" s="51" t="n">
-        <v>32512</v>
-      </c>
-      <c r="C45" s="51" t="n">
-        <v>65280</v>
-      </c>
-      <c r="D45" s="51" t="inlineStr">
-        <is>
-          <t>FF00</t>
-        </is>
-      </c>
-      <c r="E45" s="52" t="n"/>
-      <c r="F45" s="52">
+      <c r="B45" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="52" t="n">
+        <v>32768</v>
+      </c>
+      <c r="D45" s="52" t="inlineStr">
+        <is>
+          <t>8000</t>
+        </is>
+      </c>
+      <c r="E45" s="53" t="n"/>
+      <c r="F45" s="53">
         <f>$F$3*C45+$E$7</f>
         <v/>
       </c>
-      <c r="G45" s="53">
+      <c r="G45" s="54">
         <f>(E45-F45)/$H$3</f>
         <v/>
       </c>
-      <c r="H45" s="54" t="n"/>
+      <c r="H45" s="56" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="50" t="n">
+      <c r="A46" s="51" t="n">
         <v>40</v>
       </c>
-      <c r="B46" s="51" t="n">
-        <v>32639</v>
-      </c>
-      <c r="C46" s="51" t="n">
-        <v>65407</v>
-      </c>
-      <c r="D46" s="51" t="inlineStr">
-        <is>
-          <t>FF7F</t>
-        </is>
-      </c>
-      <c r="E46" s="52" t="n"/>
-      <c r="F46" s="52">
+      <c r="B46" s="52" t="n">
+        <v>4095</v>
+      </c>
+      <c r="C46" s="52" t="n">
+        <v>36863</v>
+      </c>
+      <c r="D46" s="52" t="inlineStr">
+        <is>
+          <t>8FFF</t>
+        </is>
+      </c>
+      <c r="E46" s="53" t="n"/>
+      <c r="F46" s="53">
         <f>$F$3*C46+$E$7</f>
         <v/>
       </c>
-      <c r="G46" s="53">
+      <c r="G46" s="54">
         <f>(E46-F46)/$H$3</f>
         <v/>
       </c>
@@ -2844,52 +2831,52 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="50" t="n">
+      <c r="A47" s="51" t="n">
         <v>41</v>
       </c>
-      <c r="B47" s="51" t="n">
-        <v>32640</v>
-      </c>
-      <c r="C47" s="51" t="n">
-        <v>65408</v>
-      </c>
-      <c r="D47" s="51" t="inlineStr">
-        <is>
-          <t>FF80</t>
-        </is>
-      </c>
-      <c r="E47" s="52" t="n"/>
-      <c r="F47" s="52">
+      <c r="B47" s="52" t="n">
+        <v>4096</v>
+      </c>
+      <c r="C47" s="52" t="n">
+        <v>36864</v>
+      </c>
+      <c r="D47" s="52" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="E47" s="53" t="n"/>
+      <c r="F47" s="53">
         <f>$F$3*C47+$E$7</f>
         <v/>
       </c>
-      <c r="G47" s="53">
+      <c r="G47" s="54">
         <f>(E47-F47)/$H$3</f>
         <v/>
       </c>
-      <c r="H47" s="54" t="n"/>
+      <c r="H47" s="56" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="50" t="n">
+      <c r="A48" s="51" t="n">
         <v>42</v>
       </c>
-      <c r="B48" s="51" t="n">
-        <v>32703</v>
-      </c>
-      <c r="C48" s="51" t="n">
-        <v>65471</v>
-      </c>
-      <c r="D48" s="51" t="inlineStr">
-        <is>
-          <t>FFBF</t>
-        </is>
-      </c>
-      <c r="E48" s="52" t="n"/>
-      <c r="F48" s="52">
+      <c r="B48" s="52" t="n">
+        <v>8191</v>
+      </c>
+      <c r="C48" s="52" t="n">
+        <v>40959</v>
+      </c>
+      <c r="D48" s="52" t="inlineStr">
+        <is>
+          <t>9FFF</t>
+        </is>
+      </c>
+      <c r="E48" s="53" t="n"/>
+      <c r="F48" s="53">
         <f>$F$3*C48+$E$7</f>
         <v/>
       </c>
-      <c r="G48" s="53">
+      <c r="G48" s="54">
         <f>(E48-F48)/$H$3</f>
         <v/>
       </c>
@@ -2899,52 +2886,52 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="50" t="n">
+      <c r="A49" s="51" t="n">
         <v>43</v>
       </c>
-      <c r="B49" s="51" t="n">
-        <v>32704</v>
-      </c>
-      <c r="C49" s="51" t="n">
-        <v>65472</v>
-      </c>
-      <c r="D49" s="51" t="inlineStr">
-        <is>
-          <t>FFC0</t>
-        </is>
-      </c>
-      <c r="E49" s="52" t="n"/>
-      <c r="F49" s="52">
+      <c r="B49" s="52" t="n">
+        <v>8192</v>
+      </c>
+      <c r="C49" s="52" t="n">
+        <v>40960</v>
+      </c>
+      <c r="D49" s="52" t="inlineStr">
+        <is>
+          <t>A000</t>
+        </is>
+      </c>
+      <c r="E49" s="53" t="n"/>
+      <c r="F49" s="53">
         <f>$F$3*C49+$E$7</f>
         <v/>
       </c>
-      <c r="G49" s="53">
+      <c r="G49" s="54">
         <f>(E49-F49)/$H$3</f>
         <v/>
       </c>
-      <c r="H49" s="54" t="n"/>
+      <c r="H49" s="56" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="50" t="n">
+      <c r="A50" s="51" t="n">
         <v>44</v>
       </c>
-      <c r="B50" s="51" t="n">
-        <v>32735</v>
-      </c>
-      <c r="C50" s="51" t="n">
-        <v>65503</v>
-      </c>
-      <c r="D50" s="51" t="inlineStr">
-        <is>
-          <t>FFDF</t>
-        </is>
-      </c>
-      <c r="E50" s="52" t="n"/>
-      <c r="F50" s="52">
+      <c r="B50" s="52" t="n">
+        <v>12287</v>
+      </c>
+      <c r="C50" s="52" t="n">
+        <v>45055</v>
+      </c>
+      <c r="D50" s="52" t="inlineStr">
+        <is>
+          <t>AFFF</t>
+        </is>
+      </c>
+      <c r="E50" s="53" t="n"/>
+      <c r="F50" s="53">
         <f>$F$3*C50+$E$7</f>
         <v/>
       </c>
-      <c r="G50" s="53">
+      <c r="G50" s="54">
         <f>(E50-F50)/$H$3</f>
         <v/>
       </c>
@@ -2954,52 +2941,52 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="50" t="n">
+      <c r="A51" s="51" t="n">
         <v>45</v>
       </c>
-      <c r="B51" s="51" t="n">
-        <v>32736</v>
-      </c>
-      <c r="C51" s="51" t="n">
-        <v>65504</v>
-      </c>
-      <c r="D51" s="51" t="inlineStr">
-        <is>
-          <t>FFE0</t>
-        </is>
-      </c>
-      <c r="E51" s="52" t="n"/>
-      <c r="F51" s="52">
+      <c r="B51" s="52" t="n">
+        <v>12288</v>
+      </c>
+      <c r="C51" s="52" t="n">
+        <v>45056</v>
+      </c>
+      <c r="D51" s="52" t="inlineStr">
+        <is>
+          <t>B000</t>
+        </is>
+      </c>
+      <c r="E51" s="53" t="n"/>
+      <c r="F51" s="53">
         <f>$F$3*C51+$E$7</f>
         <v/>
       </c>
-      <c r="G51" s="53">
+      <c r="G51" s="54">
         <f>(E51-F51)/$H$3</f>
         <v/>
       </c>
-      <c r="H51" s="54" t="n"/>
+      <c r="H51" s="56" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="50" t="n">
+      <c r="A52" s="51" t="n">
         <v>46</v>
       </c>
-      <c r="B52" s="51" t="n">
-        <v>32751</v>
-      </c>
-      <c r="C52" s="51" t="n">
-        <v>65519</v>
-      </c>
-      <c r="D52" s="51" t="inlineStr">
-        <is>
-          <t>FFEF</t>
-        </is>
-      </c>
-      <c r="E52" s="52" t="n"/>
-      <c r="F52" s="52">
+      <c r="B52" s="52" t="n">
+        <v>16383</v>
+      </c>
+      <c r="C52" s="52" t="n">
+        <v>49151</v>
+      </c>
+      <c r="D52" s="52" t="inlineStr">
+        <is>
+          <t>BFFF</t>
+        </is>
+      </c>
+      <c r="E52" s="53" t="n"/>
+      <c r="F52" s="53">
         <f>$F$3*C52+$E$7</f>
         <v/>
       </c>
-      <c r="G52" s="53">
+      <c r="G52" s="54">
         <f>(E52-F52)/$H$3</f>
         <v/>
       </c>
@@ -3009,52 +2996,52 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="50" t="n">
+      <c r="A53" s="51" t="n">
         <v>47</v>
       </c>
-      <c r="B53" s="51" t="n">
-        <v>32752</v>
-      </c>
-      <c r="C53" s="51" t="n">
-        <v>65520</v>
-      </c>
-      <c r="D53" s="51" t="inlineStr">
-        <is>
-          <t>FFF0</t>
-        </is>
-      </c>
-      <c r="E53" s="52" t="n"/>
-      <c r="F53" s="52">
+      <c r="B53" s="52" t="n">
+        <v>16384</v>
+      </c>
+      <c r="C53" s="52" t="n">
+        <v>49152</v>
+      </c>
+      <c r="D53" s="52" t="inlineStr">
+        <is>
+          <t>C000</t>
+        </is>
+      </c>
+      <c r="E53" s="53" t="n"/>
+      <c r="F53" s="53">
         <f>$F$3*C53+$E$7</f>
         <v/>
       </c>
-      <c r="G53" s="53">
+      <c r="G53" s="54">
         <f>(E53-F53)/$H$3</f>
         <v/>
       </c>
-      <c r="H53" s="54" t="n"/>
+      <c r="H53" s="56" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="50" t="n">
+      <c r="A54" s="51" t="n">
         <v>48</v>
       </c>
-      <c r="B54" s="51" t="n">
-        <v>32759</v>
-      </c>
-      <c r="C54" s="51" t="n">
-        <v>65527</v>
-      </c>
-      <c r="D54" s="51" t="inlineStr">
-        <is>
-          <t>FFF7</t>
-        </is>
-      </c>
-      <c r="E54" s="52" t="n"/>
-      <c r="F54" s="52">
+      <c r="B54" s="52" t="n">
+        <v>20479</v>
+      </c>
+      <c r="C54" s="52" t="n">
+        <v>53247</v>
+      </c>
+      <c r="D54" s="52" t="inlineStr">
+        <is>
+          <t>CFFF</t>
+        </is>
+      </c>
+      <c r="E54" s="53" t="n"/>
+      <c r="F54" s="53">
         <f>$F$3*C54+$E$7</f>
         <v/>
       </c>
-      <c r="G54" s="53">
+      <c r="G54" s="54">
         <f>(E54-F54)/$H$3</f>
         <v/>
       </c>
@@ -3064,52 +3051,52 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="50" t="n">
+      <c r="A55" s="51" t="n">
         <v>49</v>
       </c>
-      <c r="B55" s="51" t="n">
-        <v>32760</v>
-      </c>
-      <c r="C55" s="51" t="n">
-        <v>65528</v>
-      </c>
-      <c r="D55" s="51" t="inlineStr">
-        <is>
-          <t>FFF8</t>
-        </is>
-      </c>
-      <c r="E55" s="52" t="n"/>
-      <c r="F55" s="52">
+      <c r="B55" s="52" t="n">
+        <v>20480</v>
+      </c>
+      <c r="C55" s="52" t="n">
+        <v>53248</v>
+      </c>
+      <c r="D55" s="52" t="inlineStr">
+        <is>
+          <t>D000</t>
+        </is>
+      </c>
+      <c r="E55" s="53" t="n"/>
+      <c r="F55" s="53">
         <f>$F$3*C55+$E$7</f>
         <v/>
       </c>
-      <c r="G55" s="53">
+      <c r="G55" s="54">
         <f>(E55-F55)/$H$3</f>
         <v/>
       </c>
-      <c r="H55" s="54" t="n"/>
+      <c r="H55" s="56" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="50" t="n">
+      <c r="A56" s="51" t="n">
         <v>50</v>
       </c>
-      <c r="B56" s="51" t="n">
-        <v>32763</v>
-      </c>
-      <c r="C56" s="51" t="n">
-        <v>65531</v>
-      </c>
-      <c r="D56" s="51" t="inlineStr">
-        <is>
-          <t>FFFB</t>
-        </is>
-      </c>
-      <c r="E56" s="52" t="n"/>
-      <c r="F56" s="52">
+      <c r="B56" s="52" t="n">
+        <v>24575</v>
+      </c>
+      <c r="C56" s="52" t="n">
+        <v>57343</v>
+      </c>
+      <c r="D56" s="52" t="inlineStr">
+        <is>
+          <t>DFFF</t>
+        </is>
+      </c>
+      <c r="E56" s="53" t="n"/>
+      <c r="F56" s="53">
         <f>$F$3*C56+$E$7</f>
         <v/>
       </c>
-      <c r="G56" s="53">
+      <c r="G56" s="54">
         <f>(E56-F56)/$H$3</f>
         <v/>
       </c>
@@ -3119,55 +3106,52 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="50" t="n">
+      <c r="A57" s="51" t="n">
         <v>51</v>
       </c>
-      <c r="B57" s="51" t="n">
-        <v>32764</v>
-      </c>
-      <c r="C57" s="51" t="n">
-        <v>65532</v>
-      </c>
-      <c r="D57" s="51" t="inlineStr">
-        <is>
-          <t>FFFC</t>
-        </is>
-      </c>
-      <c r="E57" s="52" t="n"/>
-      <c r="F57" s="52">
+      <c r="B57" s="52" t="n">
+        <v>24576</v>
+      </c>
+      <c r="C57" s="52" t="n">
+        <v>57344</v>
+      </c>
+      <c r="D57" s="52" t="inlineStr">
+        <is>
+          <t>E000</t>
+        </is>
+      </c>
+      <c r="E57" s="53" t="n"/>
+      <c r="F57" s="53">
         <f>$F$3*C57+$E$7</f>
         <v/>
       </c>
-      <c r="G57" s="53">
+      <c r="G57" s="54">
         <f>(E57-F57)/$H$3</f>
         <v/>
       </c>
-      <c r="H57" s="55">
-        <f>G58-G57</f>
-        <v/>
-      </c>
+      <c r="H57" s="56" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="50" t="n">
+      <c r="A58" s="51" t="n">
         <v>52</v>
       </c>
-      <c r="B58" s="51" t="n">
-        <v>32765</v>
-      </c>
-      <c r="C58" s="51" t="n">
-        <v>65533</v>
-      </c>
-      <c r="D58" s="51" t="inlineStr">
-        <is>
-          <t>FFFD</t>
-        </is>
-      </c>
-      <c r="E58" s="52" t="n"/>
-      <c r="F58" s="52">
+      <c r="B58" s="52" t="n">
+        <v>28671</v>
+      </c>
+      <c r="C58" s="52" t="n">
+        <v>61439</v>
+      </c>
+      <c r="D58" s="52" t="inlineStr">
+        <is>
+          <t>EFFF</t>
+        </is>
+      </c>
+      <c r="E58" s="53" t="n"/>
+      <c r="F58" s="53">
         <f>$F$3*C58+$E$7</f>
         <v/>
       </c>
-      <c r="G58" s="53">
+      <c r="G58" s="54">
         <f>(E58-F58)/$H$3</f>
         <v/>
       </c>
@@ -3177,82 +3161,79 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="50" t="n">
+      <c r="A59" s="51" t="n">
         <v>53</v>
       </c>
-      <c r="B59" s="51" t="n">
-        <v>32766</v>
-      </c>
-      <c r="C59" s="51" t="n">
-        <v>65534</v>
-      </c>
-      <c r="D59" s="51" t="inlineStr">
-        <is>
-          <t>FFFE</t>
-        </is>
-      </c>
-      <c r="E59" s="52" t="n"/>
-      <c r="F59" s="52">
+      <c r="B59" s="52" t="n">
+        <v>28672</v>
+      </c>
+      <c r="C59" s="52" t="n">
+        <v>61440</v>
+      </c>
+      <c r="D59" s="52" t="inlineStr">
+        <is>
+          <t>F000</t>
+        </is>
+      </c>
+      <c r="E59" s="53" t="n"/>
+      <c r="F59" s="53">
         <f>$F$3*C59+$E$7</f>
         <v/>
       </c>
-      <c r="G59" s="53">
+      <c r="G59" s="54">
         <f>(E59-F59)/$H$3</f>
         <v/>
       </c>
-      <c r="H59" s="55">
-        <f>G60-G59</f>
-        <v/>
-      </c>
+      <c r="H59" s="57" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="56" t="n">
+      <c r="A60" s="58" t="n">
         <v>54</v>
       </c>
-      <c r="B60" s="57" t="n">
+      <c r="B60" s="59" t="n">
         <v>32767</v>
       </c>
-      <c r="C60" s="57" t="n">
+      <c r="C60" s="59" t="n">
         <v>65535</v>
       </c>
-      <c r="D60" s="57" t="inlineStr">
+      <c r="D60" s="59" t="inlineStr">
         <is>
           <t>FFFF</t>
         </is>
       </c>
-      <c r="E60" s="58" t="n"/>
-      <c r="F60" s="58">
+      <c r="E60" s="60" t="n"/>
+      <c r="F60" s="60">
         <f>$F$3*C60+$E$7</f>
         <v/>
       </c>
-      <c r="G60" s="59">
+      <c r="G60" s="61">
         <f>(E60-F60)/$H$3</f>
         <v/>
       </c>
-      <c r="H60" s="60" t="n"/>
+      <c r="H60" s="62" t="n"/>
     </row>
     <row r="61">
-      <c r="F61" s="61" t="inlineStr">
+      <c r="F61" s="63" t="inlineStr">
         <is>
           <t>+最大誤差</t>
         </is>
       </c>
-      <c r="G61" s="62">
+      <c r="G61" s="64">
         <f>MAX(G7:G60)</f>
         <v/>
       </c>
-      <c r="H61" s="63">
+      <c r="H61" s="65">
         <f>MAX(H7:H60)</f>
         <v/>
       </c>
     </row>
     <row r="62">
-      <c r="F62" s="50" t="inlineStr">
+      <c r="F62" s="51" t="inlineStr">
         <is>
           <t>-最大誤差</t>
         </is>
       </c>
-      <c r="G62" s="53">
+      <c r="G62" s="54">
         <f>MIN(G7:G60)</f>
         <v/>
       </c>
@@ -3262,29 +3243,29 @@
       </c>
     </row>
     <row r="63">
-      <c r="F63" s="50" t="inlineStr">
+      <c r="F63" s="51" t="inlineStr">
         <is>
           <t>判定基準</t>
         </is>
       </c>
-      <c r="G63" s="64" t="n">
+      <c r="G63" s="66" t="n">
         <v>0.5</v>
       </c>
-      <c r="H63" s="65" t="n">
+      <c r="H63" s="67" t="n">
         <v>0.25</v>
       </c>
     </row>
     <row r="64" ht="33.6" customHeight="1">
-      <c r="F64" s="66" t="inlineStr">
+      <c r="F64" s="68" t="inlineStr">
         <is>
           <t>判定結果</t>
         </is>
       </c>
-      <c r="G64" s="67">
+      <c r="G64" s="69">
         <f>IF((ABS(G61)&lt;G63)+(ABS(H61)&lt;H63)+(ABS(G62)&lt;G63)+(ABS(H62)&lt;H63)=4,"OK","NG")</f>
         <v/>
       </c>
-      <c r="H64" s="68" t="n"/>
+      <c r="H64" s="62" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
